--- a/order_forms/050_gift_wrapping_event_registration--order_forms.xlsx
+++ b/order_forms/050_gift_wrapping_event_registration--order_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gift_wrapping_event_date</t>
+          <t>gift_wrapping_event_date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gift Wrapping Event Date</t>
+          <t>Gift Wrapping Event Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -975,12 +975,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gift_certificate_name</t>
+          <t>gift_certificate_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gift Certificate Name</t>
+          <t>Gift Certificate Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gift_certificate_details</t>
+          <t>gift_certificate_details_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gift Certificate Details</t>
+          <t>Gift Certificate Details 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>participant_phone_number</t>
+          <t>participant_phone_number_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Participant Phone Number</t>
+          <t>Participant Phone Number 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wrap_location</t>
+          <t>wrap_location_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wrap Location</t>
+          <t>Wrap Location 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gift_certificate_name</t>
+          <t>gift_certificate_name_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gift Certificate</t>
+          <t>Gift Certificate Name 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
